--- a/Hardware/HardwareData.xlsx
+++ b/Hardware/HardwareData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\developer\Downloads\CISCO-omrezje-master\Hardware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zverm\Documents\CISCO-omrezje-master\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A52D85-3C48-4A16-8075-8EC1F70A4A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9D5330-7814-4290-82DD-F867AED5AF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5338E686-FE58-4924-B8C8-73F6880E9BEF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5338E686-FE58-4924-B8C8-73F6880E9BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
   <si>
     <t>Produc Name</t>
   </si>
@@ -152,9 +150,6 @@
     <t>Network Router</t>
   </si>
   <si>
-    <t>M-UV96</t>
-  </si>
-  <si>
     <t>PC Mouse</t>
   </si>
   <si>
@@ -227,7 +222,25 @@
     <t>HE208QB0V5Q/302/r2</t>
   </si>
   <si>
-    <t>295986-002</t>
+    <t>FOC1547Z4PY</t>
+  </si>
+  <si>
+    <t>FOC1448Y38L</t>
+  </si>
+  <si>
+    <t>FCZ161470JZ</t>
+  </si>
+  <si>
+    <t>FCZ161470JQ</t>
+  </si>
+  <si>
+    <t>CN-07MT0174261-68V3KVS-A03</t>
+  </si>
+  <si>
+    <t>M-R0067</t>
+  </si>
+  <si>
+    <t>810-005861</t>
   </si>
 </sst>
 </file>
@@ -391,7 +404,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Navadno" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -728,7 +741,7 @@
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -745,10 +758,10 @@
         <v>4</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>0</v>
@@ -775,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -785,9 +798,11 @@
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="D2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>19</v>
@@ -811,7 +826,7 @@
         <v>20</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -821,9 +836,11 @@
       <c r="B3" s="2">
         <v>24151</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3">
+        <v>23032802604</v>
+      </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>24</v>
@@ -847,7 +864,7 @@
         <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -855,16 +872,16 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -885,7 +902,7 @@
         <v>36</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -893,13 +910,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>28</v>
@@ -920,10 +937,10 @@
         <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -931,13 +948,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>28</v>
@@ -958,10 +975,10 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -969,11 +986,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>33</v>
@@ -997,7 +1016,7 @@
         <v>34</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1005,11 +1024,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>33</v>
@@ -1033,7 +1054,7 @@
         <v>34</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1043,9 +1064,11 @@
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>33</v>
@@ -1069,7 +1092,7 @@
         <v>36</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1079,9 +1102,11 @@
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>33</v>
@@ -1105,21 +1130,21 @@
         <v>36</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>28</v>
@@ -1128,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>21</v>
@@ -1140,10 +1165,10 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Hardware/HardwareData.xlsx
+++ b/Hardware/HardwareData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zverm\Documents\CISCO-omrezje-master\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9D5330-7814-4290-82DD-F867AED5AF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CED2AD-0653-401A-A524-6F6CCE5A9922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5338E686-FE58-4924-B8C8-73F6880E9BEF}"/>
   </bookViews>
@@ -836,7 +836,7 @@
       <c r="B3" s="2">
         <v>24151</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>23032802604</v>
       </c>
       <c r="D3" s="3" t="s">
